--- a/output/graficos_nacionales/plot_nacional_e_medianeta_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_medianeta_a_2020.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -15596,7 +15596,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -15780,7 +15780,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_medianeta_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_medianeta_a_2020.xlsx
@@ -2131,7 +2131,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:45</t>
+    <t xml:space="preserve">2026-09-07 12:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_medianeta_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_medianeta_a_2020.xlsx
@@ -2131,7 +2131,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:51</t>
+    <t xml:space="preserve">2026-09-08 10:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
